--- a/Public/assets/downloads/Ders Listesi.xlsx
+++ b/Public/assets/downloads/Ders Listesi.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sayfa1!$B$1:$K$243</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sayfa1!$A$1:$L$2</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
-  <si>
-    <t xml:space="preserve">Bölüm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Program </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="90">
+  <si>
+    <t xml:space="preserve">Bölümü / Ana Bilim Dalı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programı / Bilim Dalı</t>
   </si>
   <si>
     <t xml:space="preserve">Yarıyılı</t>
@@ -59,6 +59,9 @@
     <t xml:space="preserve">Derslik türü</t>
   </si>
   <si>
+    <t xml:space="preserve">Bina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bölümler</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
     <t xml:space="preserve">Derslik</t>
   </si>
   <si>
+    <t xml:space="preserve">Tirebolu Mehmet Bayrak Myo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Elektrik ve Enerji</t>
   </si>
   <si>
@@ -101,6 +107,9 @@
     <t xml:space="preserve">Bilgisayar Laboratuvarı</t>
   </si>
   <si>
+    <t xml:space="preserve">Doğankent Ek Bina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Muhasebe Ve Vergi Uygulamaları</t>
   </si>
   <si>
@@ -114,6 +123,9 @@
   </si>
   <si>
     <t xml:space="preserve">Uzaktan Eğitim Sınıfı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İletişim Fakültesi</t>
   </si>
   <si>
     <t xml:space="preserve">Yönetim ve Organizasyon</t>
@@ -436,37 +448,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -539,7 +551,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K299"/>
+  <dimension ref="A1:L299"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.76"/>
@@ -586,6 +598,9 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
@@ -3904,8 +3919,8 @@
       <c r="B299" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:K243"/>
-  <dataValidations count="8">
+  <autoFilter ref="A1:L2"/>
+  <dataValidations count="10">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K351:K1001" type="list">
       <formula1>"Derslik,Bilgisayar Laboratuvarı,Uzaktan Eğitim Sınıfı,Karma"</formula1>
       <formula2>0</formula2>
@@ -3914,7 +3929,7 @@
       <formula1>"1,2,3,4,5,6,7,8,9,10,11,12,"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B1 B351:B1001" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B351:B1001" type="list">
       <formula1>"Bilgisayar Programcılığı,Web Tasarımı ve Kodlama,Elektrik Üretim İletim ve Dağıtım,Alternatif Enerji Kaynakları Teknolojisi,Geleneksel El Sanatları,Kuyumculuk ve Takı Tasarımı,Bankacılık ve Sigortacılık Programı,Maliye,Muhasebe Ve Vergi Uygulamaları,Turiz"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3938,13 +3953,21 @@
       <formula1>Sheet2!$E$2:$E$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="1:1" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L1002" type="list">
+      <formula1>Sheet2!$F$2:$F$100</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Sayfa &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3963,103 +3986,113 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="6"/>
       <c r="H2" s="7"/>
       <c r="I2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -4068,16 +4101,16 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -4087,13 +4120,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -4104,13 +4137,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -4121,13 +4154,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -4137,13 +4170,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -4154,10 +4187,10 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -4168,10 +4201,10 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -4182,10 +4215,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -4196,10 +4229,10 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -4210,10 +4243,10 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -4224,10 +4257,10 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -4238,7 +4271,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -4249,7 +4282,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -4260,7 +4293,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -4271,7 +4304,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -4282,7 +4315,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -4293,7 +4326,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -4304,7 +4337,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -4315,7 +4348,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -4326,7 +4359,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -4337,7 +4370,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -4348,7 +4381,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -4359,7 +4392,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -4370,7 +4403,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="3"/>
@@ -4381,7 +4414,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -4392,7 +4425,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -4403,7 +4436,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -4414,7 +4447,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -4425,7 +4458,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="3"/>
@@ -4436,7 +4469,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -4447,7 +4480,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -4458,7 +4491,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -4469,7 +4502,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C38" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -4480,7 +4513,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -4491,7 +4524,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C40" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -4513,8 +4546,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/Public/assets/downloads/Ders Listesi.xlsx
+++ b/Public/assets/downloads/Ders Listesi.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" state="visible" r:id="rId3"/>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">Bilgisayar Laboratuvarı</t>
   </si>
   <si>
-    <t xml:space="preserve">Doğankent Ek Bina</t>
+    <t xml:space="preserve">Doğankent Ek Hizmet Binası</t>
   </si>
   <si>
     <t xml:space="preserve">Muhasebe Ve Vergi Uygulamaları</t>
@@ -304,7 +304,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -338,6 +338,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -382,7 +387,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -412,6 +417,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3986,7 +3995,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4005,7 +4014,7 @@
       <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4048,7 +4057,7 @@
       <c r="E3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="6"/>

--- a/Public/assets/downloads/Ders Listesi.xlsx
+++ b/Public/assets/downloads/Ders Listesi.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,6 +23,49 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Bilinmeyen Yazar</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Dersin grubu yoksa 0 yazılmalıdır.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>-228</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="90">
   <si>
@@ -50,7 +93,7 @@
     <t xml:space="preserve">Saati</t>
   </si>
   <si>
-    <t xml:space="preserve">Mevcudu</t>
+    <t xml:space="preserve">Kontenjan/Mevcut</t>
   </si>
   <si>
     <t xml:space="preserve">Hocası</t>
@@ -387,7 +430,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -417,10 +460,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -569,6 +608,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="48.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="5.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="34.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.21"/>
   </cols>
@@ -3978,7 +4018,8 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -4057,7 +4098,7 @@
       <c r="E3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="6"/>
